--- a/www/ig/fhir/core/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/www/ig/fhir/core/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -7,13 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from FR Core CodeSyst" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -27,16 +27,10 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-method-collection</t>
   </si>
   <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/ValueSet#urn:oid:2.16.840.1.113883.2.8.1.3.31</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -254,7 +248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -343,15 +337,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -369,28 +363,20 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>26</v>
-      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -409,28 +395,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/www/ig/fhir/core/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/www/ig/fhir/core/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -7,13 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from FR Core CodeSyst" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -27,10 +27,16 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-method-collection</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/ValueSet#urn:oid:2.16.840.1.113883.2.8.1.3.31</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +78,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -248,7 +254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -337,15 +343,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -363,20 +369,28 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
         <v>28</v>
+      </c>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -395,28 +409,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/www/ig/fhir/core/ValueSet-fr-core-vs-identity-method-collection.xlsx
+++ b/www/ig/fhir/core/ValueSet-fr-core-vs-identity-method-collection.xlsx
@@ -7,13 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from FR Core CodeSyst" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -27,16 +27,10 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-method-collection</t>
   </si>
   <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>http://interopsante.org/fhir/ValueSet#urn:oid:2.16.840.1.113883.2.8.1.3.31</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -254,7 +248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -343,15 +337,15 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>22</v>
@@ -369,28 +363,20 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>26</v>
-      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -409,28 +395,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
